--- a/Salla Prices.xlsx
+++ b/Salla Prices.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasser.s\Desktop\Yasser\Others\Others\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\salla-website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED5B622-84B0-4A10-853D-63D4C89A4A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0A4163-B846-403D-BB38-006B2E4911CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="638" windowWidth="21585" windowHeight="12862" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prices" sheetId="2" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Prices!$A$1:$R$213</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="89">
   <si>
     <t>Product Name</t>
   </si>
@@ -245,9 +245,6 @@
     <t>Bed Sheet (Single)</t>
   </si>
   <si>
-    <t>Carpet (Per Meter)</t>
-  </si>
-  <si>
     <t>Small Curtain</t>
   </si>
   <si>
@@ -297,6 +294,18 @@
   </si>
   <si>
     <t>Pillow Case</t>
+  </si>
+  <si>
+    <t>Machine Made Carpets (Per Meter)</t>
+  </si>
+  <si>
+    <t>Hand Tufted Carpets (Per Meter)</t>
+  </si>
+  <si>
+    <t>Handmade Carpets (Wool)</t>
+  </si>
+  <si>
+    <t>Handmade Carpets (Silk)</t>
   </si>
 </sst>
 </file>
@@ -350,803 +359,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Final Prices"/>
-      <sheetName val="Sheet2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="7">
-          <cell r="BO7">
-            <v>0.4</v>
-          </cell>
-          <cell r="BP7">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ7">
-            <v>0.7</v>
-          </cell>
-          <cell r="BR7">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="BO8">
-            <v>1</v>
-          </cell>
-          <cell r="BP8">
-            <v>1.25</v>
-          </cell>
-          <cell r="BQ8">
-            <v>1.5</v>
-          </cell>
-          <cell r="BR8">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="BP9">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ9">
-            <v>0.7</v>
-          </cell>
-          <cell r="BR9">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="BP10">
-            <v>0.4</v>
-          </cell>
-          <cell r="BQ10">
-            <v>0.5</v>
-          </cell>
-          <cell r="BR10">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="BO11">
-            <v>0.2</v>
-          </cell>
-          <cell r="BP11">
-            <v>0.3</v>
-          </cell>
-          <cell r="BQ11">
-            <v>0.35</v>
-          </cell>
-          <cell r="BR11">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="BO12">
-            <v>0.3</v>
-          </cell>
-          <cell r="BP12">
-            <v>0.4</v>
-          </cell>
-          <cell r="BQ12">
-            <v>0.5</v>
-          </cell>
-          <cell r="BR12">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="BO13">
-            <v>1</v>
-          </cell>
-          <cell r="BP13">
-            <v>1.4</v>
-          </cell>
-          <cell r="BQ13">
-            <v>1.7</v>
-          </cell>
-          <cell r="BR13">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="BO14">
-            <v>0.6</v>
-          </cell>
-          <cell r="BP14">
-            <v>0.8</v>
-          </cell>
-          <cell r="BQ14">
-            <v>1</v>
-          </cell>
-          <cell r="BR14">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="BO15">
-            <v>0.4</v>
-          </cell>
-          <cell r="BP15">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ15">
-            <v>0.7</v>
-          </cell>
-          <cell r="BR15">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="BO16">
-            <v>0.4</v>
-          </cell>
-          <cell r="BP16">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ16">
-            <v>0.8</v>
-          </cell>
-          <cell r="BR16">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="BO17">
-            <v>0.25</v>
-          </cell>
-          <cell r="BP17">
-            <v>0.35</v>
-          </cell>
-          <cell r="BQ17">
-            <v>0.45</v>
-          </cell>
-          <cell r="BR17">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="BO18">
-            <v>0.2</v>
-          </cell>
-          <cell r="BP18">
-            <v>0.25</v>
-          </cell>
-          <cell r="BQ18">
-            <v>0.3</v>
-          </cell>
-          <cell r="BR18">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="BO19">
-            <v>0.3</v>
-          </cell>
-          <cell r="BP19">
-            <v>0.5</v>
-          </cell>
-          <cell r="BQ19">
-            <v>0.6</v>
-          </cell>
-          <cell r="BR19">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="BO20">
-            <v>0.4</v>
-          </cell>
-          <cell r="BP20">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ20">
-            <v>0.7</v>
-          </cell>
-          <cell r="BR20">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="BO21">
-            <v>0.7</v>
-          </cell>
-          <cell r="BP21">
-            <v>1</v>
-          </cell>
-          <cell r="BQ21">
-            <v>1.2</v>
-          </cell>
-          <cell r="BR21">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="BO22">
-            <v>2</v>
-          </cell>
-          <cell r="BP22">
-            <v>2.5</v>
-          </cell>
-          <cell r="BQ22">
-            <v>3</v>
-          </cell>
-          <cell r="BR22">
-            <v>0.6</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="BO23">
-            <v>0.2</v>
-          </cell>
-          <cell r="BP23">
-            <v>0.3</v>
-          </cell>
-          <cell r="BQ23">
-            <v>0.4</v>
-          </cell>
-          <cell r="BR23">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="BO24">
-            <v>0.2</v>
-          </cell>
-          <cell r="BP24">
-            <v>0.5</v>
-          </cell>
-          <cell r="BQ24">
-            <v>0.6</v>
-          </cell>
-          <cell r="BR24">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="BO25">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="BO26">
-            <v>0.6</v>
-          </cell>
-          <cell r="BR26">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="BP27">
-            <v>20.8</v>
-          </cell>
-          <cell r="BQ27">
-            <v>25</v>
-          </cell>
-          <cell r="BR27">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="BO28">
-            <v>1.5</v>
-          </cell>
-          <cell r="BP28">
-            <v>1.75</v>
-          </cell>
-          <cell r="BQ28">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="BO29">
-            <v>0.2</v>
-          </cell>
-          <cell r="BP29">
-            <v>0.3</v>
-          </cell>
-          <cell r="BQ29">
-            <v>0.4</v>
-          </cell>
-          <cell r="BR29">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="BO30">
-            <v>0.4</v>
-          </cell>
-          <cell r="BP30">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ30">
-            <v>0.7</v>
-          </cell>
-          <cell r="BR30">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="BP31">
-            <v>3</v>
-          </cell>
-          <cell r="BR31">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="BO32">
-            <v>1</v>
-          </cell>
-          <cell r="BP32">
-            <v>1.25</v>
-          </cell>
-          <cell r="BQ32">
-            <v>1.5</v>
-          </cell>
-          <cell r="BR32">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="BP33">
-            <v>1.6</v>
-          </cell>
-          <cell r="BQ33">
-            <v>2</v>
-          </cell>
-          <cell r="BR33">
-            <v>0.6</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="BP34">
-            <v>2.2000000000000002</v>
-          </cell>
-          <cell r="BQ34">
-            <v>2.8</v>
-          </cell>
-          <cell r="BR34">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="BP35">
-            <v>2.7</v>
-          </cell>
-          <cell r="BQ35">
-            <v>3.2</v>
-          </cell>
-          <cell r="BR35">
-            <v>1.2</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="BO36">
-            <v>0.4</v>
-          </cell>
-          <cell r="BP36">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ36">
-            <v>0.7</v>
-          </cell>
-          <cell r="BR36">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="BO37">
-            <v>0.5</v>
-          </cell>
-          <cell r="BP37">
-            <v>0.8</v>
-          </cell>
-          <cell r="BQ37">
-            <v>1</v>
-          </cell>
-          <cell r="BR37">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="BP38">
-            <v>2.9</v>
-          </cell>
-          <cell r="BQ38">
-            <v>3.4</v>
-          </cell>
-          <cell r="BR38">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="BP39">
-            <v>4</v>
-          </cell>
-          <cell r="BQ39">
-            <v>4.9000000000000004</v>
-          </cell>
-          <cell r="BR39">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="BO40">
-            <v>0.6</v>
-          </cell>
-          <cell r="BQ40">
-            <v>1.2</v>
-          </cell>
-          <cell r="BR40">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="BO41">
-            <v>1.4</v>
-          </cell>
-          <cell r="BP41">
-            <v>1.8</v>
-          </cell>
-          <cell r="BQ41">
-            <v>2.2000000000000002</v>
-          </cell>
-          <cell r="BR41">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="BO42">
-            <v>0.7</v>
-          </cell>
-          <cell r="BQ42">
-            <v>1</v>
-          </cell>
-          <cell r="BR42">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="BO43">
-            <v>1</v>
-          </cell>
-          <cell r="BR43">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="BP44">
-            <v>1.6</v>
-          </cell>
-          <cell r="BQ44">
-            <v>1.9000000000000001</v>
-          </cell>
-          <cell r="BR44">
-            <v>0.8</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="BP45">
-            <v>2.5</v>
-          </cell>
-          <cell r="BR45">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="BP46">
-            <v>1.8</v>
-          </cell>
-          <cell r="BQ46">
-            <v>2.2000000000000002</v>
-          </cell>
-          <cell r="BR46">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="BP47">
-            <v>1.9</v>
-          </cell>
-          <cell r="BR47">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="BO48">
-            <v>0.3</v>
-          </cell>
-          <cell r="BR48">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="BO49">
-            <v>0.3</v>
-          </cell>
-          <cell r="BP49">
-            <v>0.5</v>
-          </cell>
-          <cell r="BQ49">
-            <v>0.6</v>
-          </cell>
-          <cell r="BR49">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="BO50">
-            <v>0.3</v>
-          </cell>
-          <cell r="BR50">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="BO51">
-            <v>0.3</v>
-          </cell>
-          <cell r="BR51">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="BO52">
-            <v>0.3</v>
-          </cell>
-          <cell r="BR52">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="BO62">
-            <v>0.8</v>
-          </cell>
-          <cell r="BP62">
-            <v>1.2</v>
-          </cell>
-          <cell r="BQ62">
-            <v>1.4000000000000001</v>
-          </cell>
-          <cell r="BR62">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="BO63">
-            <v>1.5</v>
-          </cell>
-          <cell r="BP63">
-            <v>2.5</v>
-          </cell>
-          <cell r="BQ63">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="BO64">
-            <v>2</v>
-          </cell>
-          <cell r="BP64">
-            <v>3</v>
-          </cell>
-          <cell r="BQ64">
-            <v>3.5</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="BO65">
-            <v>0.5</v>
-          </cell>
-          <cell r="BP65">
-            <v>0.8</v>
-          </cell>
-          <cell r="BQ65">
-            <v>1</v>
-          </cell>
-          <cell r="BR65">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="BO66">
-            <v>1.8</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="BO68">
-            <v>0.9</v>
-          </cell>
-          <cell r="BP68">
-            <v>1.2</v>
-          </cell>
-          <cell r="BQ68">
-            <v>1.4000000000000001</v>
-          </cell>
-          <cell r="BR68">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="BO69">
-            <v>1.3</v>
-          </cell>
-          <cell r="BP69">
-            <v>1.7</v>
-          </cell>
-          <cell r="BQ69">
-            <v>2</v>
-          </cell>
-          <cell r="BR69">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="BO70">
-            <v>1.7000000000000002</v>
-          </cell>
-          <cell r="BP70">
-            <v>2.2999999999999998</v>
-          </cell>
-          <cell r="BQ70">
-            <v>2.8000000000000003</v>
-          </cell>
-          <cell r="BR70">
-            <v>0.9</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="BO71">
-            <v>0.4</v>
-          </cell>
-          <cell r="BP71">
-            <v>0.7</v>
-          </cell>
-          <cell r="BQ71">
-            <v>0.9</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="BO72">
-            <v>0.5</v>
-          </cell>
-          <cell r="BR72">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="BO73">
-            <v>0.2</v>
-          </cell>
-          <cell r="BR73">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="BO74">
-            <v>0.6</v>
-          </cell>
-          <cell r="BR74">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="BO75">
-            <v>0.3</v>
-          </cell>
-          <cell r="BR75">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="BO76">
-            <v>0.5</v>
-          </cell>
-          <cell r="BP76">
-            <v>0.7</v>
-          </cell>
-          <cell r="BQ76">
-            <v>0.9</v>
-          </cell>
-          <cell r="BR76">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="BO77">
-            <v>0.3</v>
-          </cell>
-          <cell r="BP77">
-            <v>0.5</v>
-          </cell>
-          <cell r="BQ77">
-            <v>0.7</v>
-          </cell>
-          <cell r="BR77">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="BO78">
-            <v>0.2</v>
-          </cell>
-          <cell r="BQ78">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="BO79">
-            <v>0.4</v>
-          </cell>
-          <cell r="BQ79">
-            <v>0.6</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="BO80">
-            <v>1</v>
-          </cell>
-          <cell r="BQ80">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="BO81">
-            <v>1</v>
-          </cell>
-          <cell r="BQ81">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="BO82">
-            <v>1.5</v>
-          </cell>
-          <cell r="BQ82">
-            <v>2</v>
-          </cell>
-          <cell r="BR82">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="BO83">
-            <v>2</v>
-          </cell>
-          <cell r="BQ83">
-            <v>3</v>
-          </cell>
-          <cell r="BR83">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="BO84">
-            <v>0.3</v>
-          </cell>
-          <cell r="BQ84">
-            <v>0.5</v>
-          </cell>
-          <cell r="BR84">
-            <v>0.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1412,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F9F789-5046-43B1-9C3D-7BC06BA3325B}">
-  <dimension ref="A1:R214"/>
+  <dimension ref="A1:W217"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -1432,7 +644,7 @@
     <col min="18" max="18" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1488,19 +700,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
-        <f>[1]Sheet1!BO7</f>
         <v>0.4</v>
       </c>
       <c r="D2">
-        <f>C2*2</f>
         <v>0.8</v>
       </c>
       <c r="F2">
@@ -1540,71 +750,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D3">
+        <v>1.2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="V3">
         <v>2</v>
       </c>
-      <c r="C3" s="1">
-        <f>[1]Sheet1!BP7</f>
-        <v>0.6</v>
-      </c>
-      <c r="D3">
-        <f>C3*2</f>
-        <v>1.2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="W3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1">
-        <f>[1]Sheet1!BQ7</f>
         <v>0.7</v>
       </c>
       <c r="D4">
-        <f>C4*2</f>
         <v>1.4</v>
       </c>
       <c r="F4">
@@ -1643,20 +855,24 @@
       <c r="Q4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="V4">
+        <v>4</v>
+      </c>
+      <c r="W4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <f>[1]Sheet1!BR7</f>
         <v>0.2</v>
       </c>
       <c r="D5">
-        <f>C5*2</f>
         <v>0.4</v>
       </c>
       <c r="F5">
@@ -1695,20 +911,24 @@
       <c r="Q5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <f>[1]Sheet1!BO8</f>
         <v>1</v>
       </c>
       <c r="D6">
-        <f>C6*2</f>
         <v>2</v>
       </c>
       <c r="F6">
@@ -1747,20 +967,24 @@
       <c r="Q6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="W6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <f>[1]Sheet1!BP8</f>
         <v>1.25</v>
       </c>
       <c r="D7">
-        <f>C7*2</f>
         <v>2.5</v>
       </c>
       <c r="F7">
@@ -1800,21 +1024,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="D8">
         <v>3</v>
       </c>
-      <c r="C8" s="1">
-        <f>[1]Sheet1!BQ8</f>
-        <v>1.5</v>
-      </c>
-      <c r="D8">
-        <f>C8*2</f>
-        <v>3</v>
-      </c>
       <c r="F8">
         <v>1</v>
       </c>
@@ -1852,19 +1074,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1">
-        <f>[1]Sheet1!BR8</f>
         <v>0.4</v>
       </c>
       <c r="D9">
-        <f>C9*2</f>
         <v>0.8</v>
       </c>
       <c r="F9">
@@ -1904,19 +1124,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1">
-        <f>[1]Sheet1!BP9</f>
         <v>0.6</v>
       </c>
       <c r="D10">
-        <f>C10*2</f>
         <v>1.2</v>
       </c>
       <c r="F10">
@@ -1956,19 +1174,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1">
-        <f>[1]Sheet1!BQ9</f>
         <v>0.7</v>
       </c>
       <c r="D11">
-        <f>C11*2</f>
         <v>1.4</v>
       </c>
       <c r="F11">
@@ -2008,19 +1224,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1">
-        <f>[1]Sheet1!BR9</f>
         <v>0.2</v>
       </c>
       <c r="D12">
-        <f>C12*2</f>
         <v>0.4</v>
       </c>
       <c r="F12">
@@ -2060,19 +1274,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1">
-        <f>[1]Sheet1!BP10</f>
         <v>0.4</v>
       </c>
       <c r="D13">
-        <f>C13*2</f>
         <v>0.8</v>
       </c>
       <c r="F13">
@@ -2112,19 +1324,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1">
-        <f>[1]Sheet1!BQ10</f>
         <v>0.5</v>
       </c>
       <c r="D14">
-        <f>C14*2</f>
         <v>1</v>
       </c>
       <c r="F14">
@@ -2164,19 +1374,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1">
-        <f>[1]Sheet1!BR10</f>
         <v>0.1</v>
       </c>
       <c r="D15">
-        <f>C15*2</f>
         <v>0.2</v>
       </c>
       <c r="F15">
@@ -2216,19 +1424,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" s="1">
-        <f>[1]Sheet1!BO11</f>
         <v>0.2</v>
       </c>
       <c r="D16">
-        <f>C16*2</f>
         <v>0.4</v>
       </c>
       <c r="F16">
@@ -2273,14 +1479,12 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1">
-        <f>[1]Sheet1!BP11</f>
         <v>0.3</v>
       </c>
       <c r="D17">
-        <f>C17*2</f>
         <v>0.6</v>
       </c>
       <c r="F17">
@@ -2325,14 +1529,12 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1">
-        <f>[1]Sheet1!BQ11</f>
         <v>0.35</v>
       </c>
       <c r="D18">
-        <f>C18*2</f>
         <v>0.7</v>
       </c>
       <c r="F18">
@@ -2377,14 +1579,12 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1">
-        <f>[1]Sheet1!BR11</f>
         <v>0.1</v>
       </c>
       <c r="D19">
-        <f>C19*2</f>
         <v>0.2</v>
       </c>
       <c r="F19">
@@ -2429,14 +1629,12 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1">
-        <f>[1]Sheet1!BO12</f>
         <v>0.3</v>
       </c>
       <c r="D20">
-        <f>C20*2</f>
         <v>0.6</v>
       </c>
       <c r="F20">
@@ -2481,14 +1679,12 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1">
-        <f>[1]Sheet1!BP12</f>
         <v>0.4</v>
       </c>
       <c r="D21">
-        <f>C21*2</f>
         <v>0.8</v>
       </c>
       <c r="F21">
@@ -2533,14 +1729,12 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C22" s="1">
-        <f>[1]Sheet1!BQ12</f>
         <v>0.5</v>
       </c>
       <c r="D22">
-        <f>C22*2</f>
         <v>1</v>
       </c>
       <c r="F22">
@@ -2585,14 +1779,12 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" s="1">
-        <f>[1]Sheet1!BR12</f>
         <v>0.2</v>
       </c>
       <c r="D23">
-        <f>C23*2</f>
         <v>0.4</v>
       </c>
       <c r="F23">
@@ -2637,14 +1829,12 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" s="1">
-        <f>[1]Sheet1!BO13</f>
         <v>1</v>
       </c>
       <c r="D24">
-        <f>C24*2</f>
         <v>2</v>
       </c>
       <c r="F24">
@@ -2689,14 +1879,12 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1">
-        <f>[1]Sheet1!BP13</f>
         <v>1.4</v>
       </c>
       <c r="D25">
-        <f>C25*2</f>
         <v>2.8</v>
       </c>
       <c r="F25">
@@ -2741,14 +1929,12 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C26" s="1">
-        <f>[1]Sheet1!BQ13</f>
         <v>1.7</v>
       </c>
       <c r="D26">
-        <f>C26*2</f>
         <v>3.4</v>
       </c>
       <c r="F26">
@@ -2793,14 +1979,12 @@
         <v>24</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="1">
-        <f>[1]Sheet1!BR13</f>
         <v>0.4</v>
       </c>
       <c r="D27">
-        <f>C27*2</f>
         <v>0.8</v>
       </c>
       <c r="F27">
@@ -2845,14 +2029,12 @@
         <v>25</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="1">
-        <f>[1]Sheet1!BO14</f>
         <v>0.6</v>
       </c>
       <c r="D28">
-        <f>C28*2</f>
         <v>1.2</v>
       </c>
       <c r="F28">
@@ -2897,14 +2079,12 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="1">
-        <f>[1]Sheet1!BP14</f>
         <v>0.8</v>
       </c>
       <c r="D29">
-        <f>C29*2</f>
         <v>1.6</v>
       </c>
       <c r="F29">
@@ -2949,14 +2129,12 @@
         <v>25</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1">
-        <f>[1]Sheet1!BQ14</f>
         <v>1</v>
       </c>
       <c r="D30">
-        <f>C30*2</f>
         <v>2</v>
       </c>
       <c r="F30">
@@ -3001,14 +2179,12 @@
         <v>25</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" s="1">
-        <f>[1]Sheet1!BR14</f>
         <v>0.3</v>
       </c>
       <c r="D31">
-        <f>C31*2</f>
         <v>0.6</v>
       </c>
       <c r="F31">
@@ -3053,14 +2229,12 @@
         <v>26</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1">
-        <f>[1]Sheet1!BO15</f>
         <v>0.4</v>
       </c>
       <c r="D32">
-        <f>C32*2</f>
         <v>0.8</v>
       </c>
       <c r="F32">
@@ -3105,14 +2279,12 @@
         <v>26</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="1">
-        <f>[1]Sheet1!BP15</f>
         <v>0.6</v>
       </c>
       <c r="D33">
-        <f>C33*2</f>
         <v>1.2</v>
       </c>
       <c r="F33">
@@ -3157,14 +2329,12 @@
         <v>26</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C34" s="1">
-        <f>[1]Sheet1!BQ15</f>
         <v>0.7</v>
       </c>
       <c r="D34">
-        <f>C34*2</f>
         <v>1.4</v>
       </c>
       <c r="F34">
@@ -3209,14 +2379,12 @@
         <v>26</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1">
-        <f>[1]Sheet1!BR15</f>
         <v>0.2</v>
       </c>
       <c r="D35">
-        <f>C35*2</f>
         <v>0.4</v>
       </c>
       <c r="F35">
@@ -3261,14 +2429,12 @@
         <v>27</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" s="1">
-        <f>[1]Sheet1!BO16</f>
         <v>0.4</v>
       </c>
       <c r="D36">
-        <f>C36*2</f>
         <v>0.8</v>
       </c>
       <c r="F36">
@@ -3313,14 +2479,12 @@
         <v>27</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="1">
-        <f>[1]Sheet1!BP16</f>
         <v>0.6</v>
       </c>
       <c r="D37">
-        <f>C37*2</f>
         <v>1.2</v>
       </c>
       <c r="F37">
@@ -3365,14 +2529,12 @@
         <v>27</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C38" s="1">
-        <f>[1]Sheet1!BQ16</f>
         <v>0.8</v>
       </c>
       <c r="D38">
-        <f>C38*2</f>
         <v>1.6</v>
       </c>
       <c r="F38">
@@ -3417,14 +2579,12 @@
         <v>27</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" s="1">
-        <f>[1]Sheet1!BR16</f>
         <v>0.2</v>
       </c>
       <c r="D39">
-        <f>C39*2</f>
         <v>0.4</v>
       </c>
       <c r="F39">
@@ -3469,14 +2629,12 @@
         <v>28</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1">
-        <f>[1]Sheet1!BO17</f>
         <v>0.25</v>
       </c>
       <c r="D40">
-        <f>C40*2</f>
         <v>0.5</v>
       </c>
       <c r="F40">
@@ -3521,14 +2679,12 @@
         <v>28</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="1">
-        <f>[1]Sheet1!BP17</f>
         <v>0.35</v>
       </c>
       <c r="D41">
-        <f>C41*2</f>
         <v>0.7</v>
       </c>
       <c r="F41">
@@ -3573,14 +2729,12 @@
         <v>28</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C42" s="1">
-        <f>[1]Sheet1!BQ17</f>
         <v>0.45</v>
       </c>
       <c r="D42">
-        <f>C42*2</f>
         <v>0.9</v>
       </c>
       <c r="F42">
@@ -3625,14 +2779,12 @@
         <v>28</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43" s="1">
-        <f>[1]Sheet1!BR17</f>
         <v>0.1</v>
       </c>
       <c r="D43">
-        <f>C43*2</f>
         <v>0.2</v>
       </c>
       <c r="F43">
@@ -3677,14 +2829,12 @@
         <v>29</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1">
-        <f>[1]Sheet1!BO18</f>
         <v>0.2</v>
       </c>
       <c r="D44">
-        <f>C44*2</f>
         <v>0.4</v>
       </c>
       <c r="F44">
@@ -3729,14 +2879,12 @@
         <v>29</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" s="1">
-        <f>[1]Sheet1!BP18</f>
         <v>0.25</v>
       </c>
       <c r="D45">
-        <f>C45*2</f>
         <v>0.5</v>
       </c>
       <c r="F45">
@@ -3781,14 +2929,12 @@
         <v>29</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1">
-        <f>[1]Sheet1!BQ18</f>
         <v>0.3</v>
       </c>
       <c r="D46">
-        <f>C46*2</f>
         <v>0.6</v>
       </c>
       <c r="F46">
@@ -3833,14 +2979,12 @@
         <v>29</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47" s="1">
-        <f>[1]Sheet1!BR18</f>
         <v>0.1</v>
       </c>
       <c r="D47">
-        <f>C47*2</f>
         <v>0.2</v>
       </c>
       <c r="F47">
@@ -3885,14 +3029,12 @@
         <v>30</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" s="1">
-        <f>[1]Sheet1!BO19</f>
         <v>0.3</v>
       </c>
       <c r="D48">
-        <f>C48*2</f>
         <v>0.6</v>
       </c>
       <c r="F48">
@@ -3937,14 +3079,12 @@
         <v>30</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="1">
-        <f>[1]Sheet1!BP19</f>
         <v>0.5</v>
       </c>
       <c r="D49">
-        <f>C49*2</f>
         <v>1</v>
       </c>
       <c r="F49">
@@ -3989,14 +3129,12 @@
         <v>30</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C50" s="1">
-        <f>[1]Sheet1!BQ19</f>
         <v>0.6</v>
       </c>
       <c r="D50">
-        <f>C50*2</f>
         <v>1.2</v>
       </c>
       <c r="F50">
@@ -4041,14 +3179,12 @@
         <v>30</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C51" s="1">
-        <f>[1]Sheet1!BR19</f>
         <v>0.2</v>
       </c>
       <c r="D51">
-        <f>C51*2</f>
         <v>0.4</v>
       </c>
       <c r="F51">
@@ -4093,14 +3229,12 @@
         <v>31</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52" s="1">
-        <f>[1]Sheet1!BO20</f>
         <v>0.4</v>
       </c>
       <c r="D52">
-        <f>C52*2</f>
         <v>0.8</v>
       </c>
       <c r="F52">
@@ -4145,14 +3279,12 @@
         <v>31</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" s="1">
-        <f>[1]Sheet1!BP20</f>
         <v>0.6</v>
       </c>
       <c r="D53">
-        <f>C53*2</f>
         <v>1.2</v>
       </c>
       <c r="F53">
@@ -4197,14 +3329,12 @@
         <v>31</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C54" s="1">
-        <f>[1]Sheet1!BQ20</f>
         <v>0.7</v>
       </c>
       <c r="D54">
-        <f>C54*2</f>
         <v>1.4</v>
       </c>
       <c r="F54">
@@ -4249,14 +3379,12 @@
         <v>31</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C55" s="1">
-        <f>[1]Sheet1!BR20</f>
         <v>0.1</v>
       </c>
       <c r="D55">
-        <f>C55*2</f>
         <v>0.2</v>
       </c>
       <c r="F55">
@@ -4301,14 +3429,12 @@
         <v>32</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" s="1">
-        <f>[1]Sheet1!BO21</f>
         <v>0.7</v>
       </c>
       <c r="D56">
-        <f>C56*2</f>
         <v>1.4</v>
       </c>
       <c r="F56">
@@ -4353,14 +3479,12 @@
         <v>32</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" s="1">
-        <f>[1]Sheet1!BP21</f>
         <v>1</v>
       </c>
       <c r="D57">
-        <f>C57*2</f>
         <v>2</v>
       </c>
       <c r="F57">
@@ -4405,14 +3529,12 @@
         <v>32</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C58" s="1">
-        <f>[1]Sheet1!BQ21</f>
         <v>1.2</v>
       </c>
       <c r="D58">
-        <f>C58*2</f>
         <v>2.4</v>
       </c>
       <c r="F58">
@@ -4457,14 +3579,12 @@
         <v>32</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59" s="1">
-        <f>[1]Sheet1!BR21</f>
         <v>0.4</v>
       </c>
       <c r="D59">
-        <f>C59*2</f>
         <v>0.8</v>
       </c>
       <c r="F59">
@@ -4509,14 +3629,12 @@
         <v>33</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60" s="1">
-        <f>[1]Sheet1!BO22</f>
         <v>2</v>
       </c>
       <c r="D60">
-        <f>C60*2</f>
         <v>4</v>
       </c>
       <c r="F60">
@@ -4561,14 +3679,12 @@
         <v>33</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" s="1">
-        <f>[1]Sheet1!BP22</f>
         <v>2.5</v>
       </c>
       <c r="D61">
-        <f>C61*2</f>
         <v>5</v>
       </c>
       <c r="F61">
@@ -4613,14 +3729,12 @@
         <v>33</v>
       </c>
       <c r="B62">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1">
         <v>3</v>
       </c>
-      <c r="C62" s="1">
-        <f>[1]Sheet1!BQ22</f>
-        <v>3</v>
-      </c>
       <c r="D62">
-        <f>C62*2</f>
         <v>6</v>
       </c>
       <c r="F62">
@@ -4665,14 +3779,12 @@
         <v>33</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C63" s="1">
-        <f>[1]Sheet1!BR22</f>
         <v>0.6</v>
       </c>
       <c r="D63">
-        <f>C63*2</f>
         <v>1.2</v>
       </c>
       <c r="F63">
@@ -4717,14 +3829,12 @@
         <v>34</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64" s="1">
-        <f>[1]Sheet1!BO23</f>
         <v>0.2</v>
       </c>
       <c r="D64">
-        <f>C64*2</f>
         <v>0.4</v>
       </c>
       <c r="F64">
@@ -4769,14 +3879,12 @@
         <v>34</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" s="1">
-        <f>[1]Sheet1!BP23</f>
         <v>0.3</v>
       </c>
       <c r="D65">
-        <f>C65*2</f>
         <v>0.6</v>
       </c>
       <c r="F65">
@@ -4821,14 +3929,12 @@
         <v>34</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C66" s="1">
-        <f>[1]Sheet1!BQ23</f>
         <v>0.4</v>
       </c>
       <c r="D66">
-        <f>C66*2</f>
         <v>0.8</v>
       </c>
       <c r="F66">
@@ -4873,14 +3979,12 @@
         <v>34</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C67" s="1">
-        <f>[1]Sheet1!BR23</f>
         <v>0.1</v>
       </c>
       <c r="D67">
-        <f>C67*2</f>
         <v>0.2</v>
       </c>
       <c r="F67">
@@ -4925,14 +4029,12 @@
         <v>35</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68" s="1">
-        <f>[1]Sheet1!BO24</f>
         <v>0.2</v>
       </c>
       <c r="D68">
-        <f>C68*2</f>
         <v>0.4</v>
       </c>
       <c r="F68">
@@ -4977,14 +4079,12 @@
         <v>35</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" s="1">
-        <f>[1]Sheet1!BP24</f>
         <v>0.5</v>
       </c>
       <c r="D69">
-        <f>C69*2</f>
         <v>1</v>
       </c>
       <c r="F69">
@@ -5029,14 +4129,12 @@
         <v>35</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C70" s="1">
-        <f>[1]Sheet1!BQ24</f>
         <v>0.6</v>
       </c>
       <c r="D70">
-        <f>C70*2</f>
         <v>1.2</v>
       </c>
       <c r="F70">
@@ -5081,14 +4179,12 @@
         <v>35</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C71" s="1">
-        <f>[1]Sheet1!BR24</f>
         <v>0.2</v>
       </c>
       <c r="D71">
-        <f>C71*2</f>
         <v>0.4</v>
       </c>
       <c r="F71">
@@ -5133,14 +4229,12 @@
         <v>36</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72" s="1">
-        <f>[1]Sheet1!BO25</f>
         <v>1</v>
       </c>
       <c r="D72">
-        <f>C72*2</f>
         <v>2</v>
       </c>
       <c r="F72">
@@ -5185,14 +4279,12 @@
         <v>37</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" s="1">
-        <f>[1]Sheet1!BO26</f>
         <v>0.6</v>
       </c>
       <c r="D73">
-        <f>C73*2</f>
         <v>1.2</v>
       </c>
       <c r="F73">
@@ -5237,14 +4329,12 @@
         <v>37</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C74" s="1">
-        <f>[1]Sheet1!BR26</f>
         <v>0.5</v>
       </c>
       <c r="D74">
-        <f>C74*2</f>
         <v>1</v>
       </c>
       <c r="F74">
@@ -5289,14 +4379,12 @@
         <v>38</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" s="1">
-        <f>[1]Sheet1!BP27</f>
         <v>20.8</v>
       </c>
       <c r="D75">
-        <f>C75*2</f>
         <v>41.6</v>
       </c>
       <c r="F75">
@@ -5341,14 +4429,12 @@
         <v>38</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C76" s="1">
-        <f>[1]Sheet1!BQ27</f>
         <v>25</v>
       </c>
       <c r="D76">
-        <f>C76*2</f>
         <v>50</v>
       </c>
       <c r="F76">
@@ -5393,14 +4479,12 @@
         <v>38</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77" s="1">
-        <f>[1]Sheet1!BR27</f>
         <v>5</v>
       </c>
       <c r="D77">
-        <f>C77*2</f>
         <v>10</v>
       </c>
       <c r="F77">
@@ -5445,14 +4529,12 @@
         <v>39</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" s="1">
-        <f>[1]Sheet1!BO28</f>
         <v>1.5</v>
       </c>
       <c r="D78">
-        <f>C78*2</f>
         <v>3</v>
       </c>
       <c r="F78">
@@ -5497,14 +4579,12 @@
         <v>39</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="1">
-        <f>[1]Sheet1!BP28</f>
         <v>1.75</v>
       </c>
       <c r="D79">
-        <f>C79*2</f>
         <v>3.5</v>
       </c>
       <c r="F79">
@@ -5549,14 +4629,12 @@
         <v>39</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C80" s="1">
-        <f>[1]Sheet1!BQ28</f>
         <v>2</v>
       </c>
       <c r="D80">
-        <f>C80*2</f>
         <v>4</v>
       </c>
       <c r="F80">
@@ -5601,14 +4679,12 @@
         <v>40</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" s="1">
-        <f>[1]Sheet1!BO29</f>
         <v>0.2</v>
       </c>
       <c r="D81">
-        <f>C81*2</f>
         <v>0.4</v>
       </c>
       <c r="F81">
@@ -5653,14 +4729,12 @@
         <v>40</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" s="1">
-        <f>[1]Sheet1!BP29</f>
         <v>0.3</v>
       </c>
       <c r="D82">
-        <f>C82*2</f>
         <v>0.6</v>
       </c>
       <c r="F82">
@@ -5705,14 +4779,12 @@
         <v>40</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C83" s="1">
-        <f>[1]Sheet1!BQ29</f>
         <v>0.4</v>
       </c>
       <c r="D83">
-        <f>C83*2</f>
         <v>0.8</v>
       </c>
       <c r="F83">
@@ -5757,14 +4829,12 @@
         <v>40</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C84" s="1">
-        <f>[1]Sheet1!BR29</f>
         <v>0.1</v>
       </c>
       <c r="D84">
-        <f>C84*2</f>
         <v>0.2</v>
       </c>
       <c r="F84">
@@ -5809,14 +4879,12 @@
         <v>41</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85" s="1">
-        <f>[1]Sheet1!BO30</f>
         <v>0.4</v>
       </c>
       <c r="D85">
-        <f>C85*2</f>
         <v>0.8</v>
       </c>
       <c r="F85">
@@ -5861,14 +4929,12 @@
         <v>41</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" s="1">
-        <f>[1]Sheet1!BP30</f>
         <v>0.6</v>
       </c>
       <c r="D86">
-        <f>C86*2</f>
         <v>1.2</v>
       </c>
       <c r="F86">
@@ -5913,14 +4979,12 @@
         <v>41</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C87" s="1">
-        <f>[1]Sheet1!BQ30</f>
         <v>0.7</v>
       </c>
       <c r="D87">
-        <f>C87*2</f>
         <v>1.4</v>
       </c>
       <c r="F87">
@@ -5965,14 +5029,12 @@
         <v>41</v>
       </c>
       <c r="B88">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C88" s="1">
-        <f>[1]Sheet1!BR30</f>
         <v>0.2</v>
       </c>
       <c r="D88">
-        <f>C88*2</f>
         <v>0.4</v>
       </c>
       <c r="F88">
@@ -6017,14 +5079,12 @@
         <v>42</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" s="1">
-        <f>[1]Sheet1!BP31</f>
         <v>3</v>
       </c>
       <c r="D89">
-        <f>C89*2</f>
         <v>6</v>
       </c>
       <c r="F89">
@@ -6069,14 +5129,12 @@
         <v>42</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C90" s="1">
-        <f>[1]Sheet1!BR31</f>
         <v>0.4</v>
       </c>
       <c r="D90">
-        <f>C90*2</f>
         <v>0.8</v>
       </c>
       <c r="F90">
@@ -6121,14 +5179,12 @@
         <v>43</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91" s="1">
-        <f>[1]Sheet1!BO32</f>
         <v>1</v>
       </c>
       <c r="D91">
-        <f>C91*2</f>
         <v>2</v>
       </c>
       <c r="F91">
@@ -6173,14 +5229,12 @@
         <v>43</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" s="1">
-        <f>[1]Sheet1!BP32</f>
         <v>1.25</v>
       </c>
       <c r="D92">
-        <f>C92*2</f>
         <v>2.5</v>
       </c>
       <c r="F92">
@@ -6225,14 +5279,12 @@
         <v>43</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C93" s="1">
-        <f>[1]Sheet1!BQ32</f>
         <v>1.5</v>
       </c>
       <c r="D93">
-        <f>C93*2</f>
         <v>3</v>
       </c>
       <c r="F93">
@@ -6277,14 +5329,12 @@
         <v>43</v>
       </c>
       <c r="B94">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C94" s="1">
-        <f>[1]Sheet1!BR32</f>
         <v>0.5</v>
       </c>
       <c r="D94">
-        <f>C94*2</f>
         <v>1</v>
       </c>
       <c r="F94">
@@ -6329,14 +5379,12 @@
         <v>44</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" s="1">
-        <f>[1]Sheet1!BP33</f>
         <v>1.6</v>
       </c>
       <c r="D95">
-        <f>C95*2</f>
         <v>3.2</v>
       </c>
       <c r="F95">
@@ -6381,14 +5429,12 @@
         <v>44</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C96" s="1">
-        <f>[1]Sheet1!BQ33</f>
         <v>2</v>
       </c>
       <c r="D96">
-        <f>C96*2</f>
         <v>4</v>
       </c>
       <c r="F96">
@@ -6433,14 +5479,12 @@
         <v>44</v>
       </c>
       <c r="B97">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C97" s="1">
-        <f>[1]Sheet1!BR33</f>
         <v>0.6</v>
       </c>
       <c r="D97">
-        <f>C97*2</f>
         <v>1.2</v>
       </c>
       <c r="F97">
@@ -6485,14 +5529,12 @@
         <v>45</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" s="1">
-        <f>[1]Sheet1!BP34</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="D98">
-        <f>C98*2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="F98">
@@ -6537,14 +5579,12 @@
         <v>45</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C99" s="1">
-        <f>[1]Sheet1!BQ34</f>
         <v>2.8</v>
       </c>
       <c r="D99">
-        <f>C99*2</f>
         <v>5.6</v>
       </c>
       <c r="F99">
@@ -6589,14 +5629,12 @@
         <v>45</v>
       </c>
       <c r="B100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C100" s="1">
-        <f>[1]Sheet1!BR34</f>
         <v>1</v>
       </c>
       <c r="D100">
-        <f>C100*2</f>
         <v>2</v>
       </c>
       <c r="F100">
@@ -6641,14 +5679,12 @@
         <v>46</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" s="1">
-        <f>[1]Sheet1!BP35</f>
         <v>2.7</v>
       </c>
       <c r="D101">
-        <f>C101*2</f>
         <v>5.4</v>
       </c>
       <c r="F101">
@@ -6693,14 +5729,12 @@
         <v>46</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C102" s="1">
-        <f>[1]Sheet1!BQ35</f>
         <v>3.2</v>
       </c>
       <c r="D102">
-        <f>C102*2</f>
         <v>6.4</v>
       </c>
       <c r="F102">
@@ -6745,14 +5779,12 @@
         <v>46</v>
       </c>
       <c r="B103">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C103" s="1">
-        <f>[1]Sheet1!BR35</f>
         <v>1.2</v>
       </c>
       <c r="D103">
-        <f>C103*2</f>
         <v>2.4</v>
       </c>
       <c r="F103">
@@ -6797,14 +5829,12 @@
         <v>47</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C104" s="1">
-        <f>[1]Sheet1!BO36</f>
         <v>0.4</v>
       </c>
       <c r="D104">
-        <f>C104*2</f>
         <v>0.8</v>
       </c>
       <c r="F104">
@@ -6849,14 +5879,12 @@
         <v>47</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" s="1">
-        <f>[1]Sheet1!BP36</f>
         <v>0.6</v>
       </c>
       <c r="D105">
-        <f>C105*2</f>
         <v>1.2</v>
       </c>
       <c r="F105">
@@ -6901,14 +5929,12 @@
         <v>47</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C106" s="1">
-        <f>[1]Sheet1!BQ36</f>
         <v>0.7</v>
       </c>
       <c r="D106">
-        <f>C106*2</f>
         <v>1.4</v>
       </c>
       <c r="F106">
@@ -6953,14 +5979,12 @@
         <v>47</v>
       </c>
       <c r="B107">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C107" s="1">
-        <f>[1]Sheet1!BR36</f>
         <v>0.2</v>
       </c>
       <c r="D107">
-        <f>C107*2</f>
         <v>0.4</v>
       </c>
       <c r="F107">
@@ -7005,14 +6029,12 @@
         <v>48</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C108" s="1">
-        <f>[1]Sheet1!BO37</f>
         <v>0.5</v>
       </c>
       <c r="D108">
-        <f>C108*2</f>
         <v>1</v>
       </c>
       <c r="F108">
@@ -7057,14 +6079,12 @@
         <v>48</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" s="1">
-        <f>[1]Sheet1!BP37</f>
         <v>0.8</v>
       </c>
       <c r="D109">
-        <f>C109*2</f>
         <v>1.6</v>
       </c>
       <c r="F109">
@@ -7109,14 +6129,12 @@
         <v>48</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C110" s="1">
-        <f>[1]Sheet1!BQ37</f>
         <v>1</v>
       </c>
       <c r="D110">
-        <f>C110*2</f>
         <v>2</v>
       </c>
       <c r="F110">
@@ -7161,14 +6179,12 @@
         <v>48</v>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C111" s="1">
-        <f>[1]Sheet1!BR37</f>
         <v>0.3</v>
       </c>
       <c r="D111">
-        <f>C111*2</f>
         <v>0.6</v>
       </c>
       <c r="F111">
@@ -7213,14 +6229,12 @@
         <v>49</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" s="1">
-        <f>[1]Sheet1!BP38</f>
         <v>2.9</v>
       </c>
       <c r="D112">
-        <f>C112*2</f>
         <v>5.8</v>
       </c>
       <c r="F112">
@@ -7265,14 +6279,12 @@
         <v>49</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C113" s="1">
-        <f>[1]Sheet1!BQ38</f>
         <v>3.4</v>
       </c>
       <c r="D113">
-        <f>C113*2</f>
         <v>6.8</v>
       </c>
       <c r="F113">
@@ -7317,14 +6329,12 @@
         <v>49</v>
       </c>
       <c r="B114">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C114" s="1">
-        <f>[1]Sheet1!BR38</f>
         <v>1</v>
       </c>
       <c r="D114">
-        <f>C114*2</f>
         <v>2</v>
       </c>
       <c r="F114">
@@ -7369,14 +6379,12 @@
         <v>50</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115" s="1">
-        <f>[1]Sheet1!BP39</f>
         <v>4</v>
       </c>
       <c r="D115">
-        <f>C115*2</f>
         <v>8</v>
       </c>
       <c r="F115">
@@ -7421,14 +6429,12 @@
         <v>50</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C116" s="1">
-        <f>[1]Sheet1!BQ39</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="D116">
-        <f>C116*2</f>
         <v>9.8000000000000007</v>
       </c>
       <c r="F116">
@@ -7473,14 +6479,12 @@
         <v>50</v>
       </c>
       <c r="B117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C117" s="1">
-        <f>[1]Sheet1!BR39</f>
         <v>2</v>
       </c>
       <c r="D117">
-        <f>C117*2</f>
         <v>4</v>
       </c>
       <c r="F117">
@@ -7525,14 +6529,12 @@
         <v>51</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C118" s="1">
-        <f>[1]Sheet1!BO40</f>
         <v>0.6</v>
       </c>
       <c r="D118">
-        <f>C118*2</f>
         <v>1.2</v>
       </c>
       <c r="F118">
@@ -7577,14 +6579,12 @@
         <v>51</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C119" s="1">
-        <f>[1]Sheet1!BQ40</f>
         <v>1.2</v>
       </c>
       <c r="D119">
-        <f>C119*2</f>
         <v>2.4</v>
       </c>
       <c r="F119">
@@ -7629,14 +6629,12 @@
         <v>51</v>
       </c>
       <c r="B120">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C120" s="1">
-        <f>[1]Sheet1!BR40</f>
         <v>0.4</v>
       </c>
       <c r="D120">
-        <f>C120*2</f>
         <v>0.8</v>
       </c>
       <c r="F120">
@@ -7681,14 +6679,12 @@
         <v>52</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C121" s="1">
-        <f>[1]Sheet1!BO41</f>
         <v>1.4</v>
       </c>
       <c r="D121">
-        <f>C121*2</f>
         <v>2.8</v>
       </c>
       <c r="F121">
@@ -7733,14 +6729,12 @@
         <v>52</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1">
-        <f>[1]Sheet1!BP41</f>
         <v>1.8</v>
       </c>
       <c r="D122">
-        <f>C122*2</f>
         <v>3.6</v>
       </c>
       <c r="F122">
@@ -7785,14 +6779,12 @@
         <v>52</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C123" s="1">
-        <f>[1]Sheet1!BQ41</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="D123">
-        <f>C123*2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="F123">
@@ -7837,14 +6829,12 @@
         <v>52</v>
       </c>
       <c r="B124">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C124" s="1">
-        <f>[1]Sheet1!BR41</f>
         <v>0.7</v>
       </c>
       <c r="D124">
-        <f>C124*2</f>
         <v>1.4</v>
       </c>
       <c r="F124">
@@ -7889,14 +6879,12 @@
         <v>53</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C125" s="1">
-        <f>[1]Sheet1!BO42</f>
         <v>0.7</v>
       </c>
       <c r="D125">
-        <f>C125*2</f>
         <v>1.4</v>
       </c>
       <c r="F125">
@@ -7941,14 +6929,12 @@
         <v>53</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C126" s="1">
-        <f>[1]Sheet1!BQ42</f>
         <v>1</v>
       </c>
       <c r="D126">
-        <f>C126*2</f>
         <v>2</v>
       </c>
       <c r="F126">
@@ -7993,14 +6979,12 @@
         <v>53</v>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C127" s="1">
-        <f>[1]Sheet1!BR42</f>
         <v>0.3</v>
       </c>
       <c r="D127">
-        <f>C127*2</f>
         <v>0.6</v>
       </c>
       <c r="F127">
@@ -8045,14 +7029,12 @@
         <v>54</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128" s="1">
-        <f>[1]Sheet1!BO43</f>
         <v>1</v>
       </c>
       <c r="D128">
-        <f>C128*2</f>
         <v>2</v>
       </c>
       <c r="F128">
@@ -8097,14 +7079,12 @@
         <v>54</v>
       </c>
       <c r="B129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C129" s="1">
-        <f>[1]Sheet1!BR43</f>
         <v>0.5</v>
       </c>
       <c r="D129">
-        <f>C129*2</f>
         <v>1</v>
       </c>
       <c r="F129">
@@ -8149,14 +7129,12 @@
         <v>55</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130" s="1">
-        <f>[1]Sheet1!BP44</f>
         <v>1.6</v>
       </c>
       <c r="D130">
-        <f>C130*2</f>
         <v>3.2</v>
       </c>
       <c r="F130">
@@ -8201,14 +7179,12 @@
         <v>55</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C131" s="1">
-        <f>[1]Sheet1!BQ44</f>
         <v>1.9000000000000001</v>
       </c>
       <c r="D131">
-        <f>C131*2</f>
         <v>3.8000000000000003</v>
       </c>
       <c r="F131">
@@ -8253,14 +7229,12 @@
         <v>55</v>
       </c>
       <c r="B132">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C132" s="1">
-        <f>[1]Sheet1!BR44</f>
         <v>0.8</v>
       </c>
       <c r="D132">
-        <f>C132*2</f>
         <v>1.6</v>
       </c>
       <c r="F132">
@@ -8305,14 +7279,12 @@
         <v>56</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C133" s="1">
-        <f>[1]Sheet1!BP45</f>
         <v>2.5</v>
       </c>
       <c r="D133">
-        <f>C133*2</f>
         <v>5</v>
       </c>
       <c r="F133">
@@ -8357,14 +7329,12 @@
         <v>56</v>
       </c>
       <c r="B134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C134" s="1">
-        <f>[1]Sheet1!BR45</f>
         <v>1</v>
       </c>
       <c r="D134">
-        <f>C134*2</f>
         <v>2</v>
       </c>
       <c r="F134">
@@ -8409,14 +7379,12 @@
         <v>57</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135" s="1">
-        <f>[1]Sheet1!BP46</f>
         <v>1.8</v>
       </c>
       <c r="D135">
-        <f>C135*2</f>
         <v>3.6</v>
       </c>
       <c r="F135">
@@ -8461,14 +7429,12 @@
         <v>57</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C136" s="1">
-        <f>[1]Sheet1!BQ46</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="D136">
-        <f>C136*2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="F136">
@@ -8513,14 +7479,12 @@
         <v>57</v>
       </c>
       <c r="B137">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C137" s="1">
-        <f>[1]Sheet1!BR46</f>
         <v>1</v>
       </c>
       <c r="D137">
-        <f>C137*2</f>
         <v>2</v>
       </c>
       <c r="F137">
@@ -8565,14 +7529,12 @@
         <v>58</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138" s="1">
-        <f>[1]Sheet1!BP47</f>
         <v>1.9</v>
       </c>
       <c r="D138">
-        <f>C138*2</f>
         <v>3.8</v>
       </c>
       <c r="F138">
@@ -8617,14 +7579,12 @@
         <v>58</v>
       </c>
       <c r="B139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C139" s="1">
-        <f>[1]Sheet1!BR47</f>
         <v>1</v>
       </c>
       <c r="D139">
-        <f>C139*2</f>
         <v>2</v>
       </c>
       <c r="F139">
@@ -8669,14 +7629,12 @@
         <v>59</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C140" s="1">
-        <f>[1]Sheet1!BO48</f>
         <v>0.3</v>
       </c>
       <c r="D140">
-        <f>C140*2</f>
         <v>0.6</v>
       </c>
       <c r="F140">
@@ -8721,14 +7679,12 @@
         <v>59</v>
       </c>
       <c r="B141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C141" s="1">
-        <f>[1]Sheet1!BR48</f>
         <v>0.1</v>
       </c>
       <c r="D141">
-        <f>C141*2</f>
         <v>0.2</v>
       </c>
       <c r="F141">
@@ -8773,14 +7729,12 @@
         <v>60</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C142" s="1">
-        <f>[1]Sheet1!BO49</f>
         <v>0.3</v>
       </c>
       <c r="D142">
-        <f>C142*2</f>
         <v>0.6</v>
       </c>
       <c r="F142">
@@ -8825,14 +7779,12 @@
         <v>60</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C143" s="1">
-        <f>[1]Sheet1!BP49</f>
         <v>0.5</v>
       </c>
       <c r="D143">
-        <f>C143*2</f>
         <v>1</v>
       </c>
       <c r="F143">
@@ -8877,14 +7829,12 @@
         <v>60</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C144" s="1">
-        <f>[1]Sheet1!BQ49</f>
         <v>0.6</v>
       </c>
       <c r="D144">
-        <f>C144*2</f>
         <v>1.2</v>
       </c>
       <c r="F144">
@@ -8929,14 +7879,12 @@
         <v>60</v>
       </c>
       <c r="B145">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C145" s="1">
-        <f>[1]Sheet1!BR49</f>
         <v>0.1</v>
       </c>
       <c r="D145">
-        <f>C145*2</f>
         <v>0.2</v>
       </c>
       <c r="F145">
@@ -8981,14 +7929,12 @@
         <v>61</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C146" s="1">
-        <f>[1]Sheet1!BO50</f>
         <v>0.3</v>
       </c>
       <c r="D146">
-        <f>C146*2</f>
         <v>0.6</v>
       </c>
       <c r="F146">
@@ -9033,14 +7979,12 @@
         <v>61</v>
       </c>
       <c r="B147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C147" s="1">
-        <f>[1]Sheet1!BR50</f>
         <v>0.1</v>
       </c>
       <c r="D147">
-        <f>C147*2</f>
         <v>0.2</v>
       </c>
       <c r="F147">
@@ -9085,14 +8029,12 @@
         <v>62</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C148" s="1">
-        <f>[1]Sheet1!BO51</f>
         <v>0.3</v>
       </c>
       <c r="D148">
-        <f>C148*2</f>
         <v>0.6</v>
       </c>
       <c r="F148">
@@ -9137,14 +8079,12 @@
         <v>62</v>
       </c>
       <c r="B149">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C149" s="1">
-        <f>[1]Sheet1!BR51</f>
         <v>0.1</v>
       </c>
       <c r="D149">
-        <f>C149*2</f>
         <v>0.2</v>
       </c>
       <c r="F149">
@@ -9189,14 +8129,12 @@
         <v>63</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C150" s="1">
-        <f>[1]Sheet1!BO52</f>
         <v>0.3</v>
       </c>
       <c r="D150">
-        <f>C150*2</f>
         <v>0.6</v>
       </c>
       <c r="F150">
@@ -9241,14 +8179,12 @@
         <v>63</v>
       </c>
       <c r="B151">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C151" s="1">
-        <f>[1]Sheet1!BR52</f>
         <v>0.1</v>
       </c>
       <c r="D151">
-        <f>C151*2</f>
         <v>0.2</v>
       </c>
       <c r="F151">
@@ -9293,14 +8229,12 @@
         <v>64</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C152" s="1">
-        <f>[1]Sheet1!BO62</f>
         <v>0.8</v>
       </c>
       <c r="D152">
-        <f>C152*2</f>
         <v>1.6</v>
       </c>
       <c r="F152">
@@ -9345,14 +8279,12 @@
         <v>64</v>
       </c>
       <c r="B153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C153" s="1">
-        <f>[1]Sheet1!BP62</f>
         <v>1.2</v>
       </c>
       <c r="D153">
-        <f>C153*2</f>
         <v>2.4</v>
       </c>
       <c r="F153">
@@ -9397,14 +8329,12 @@
         <v>64</v>
       </c>
       <c r="B154">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C154" s="1">
-        <f>[1]Sheet1!BQ62</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="D154">
-        <f>C154*2</f>
         <v>2.8000000000000003</v>
       </c>
       <c r="F154">
@@ -9449,14 +8379,12 @@
         <v>64</v>
       </c>
       <c r="B155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C155" s="1">
-        <f>[1]Sheet1!BR62</f>
         <v>0.4</v>
       </c>
       <c r="D155">
-        <f>C155*2</f>
         <v>0.8</v>
       </c>
       <c r="F155">
@@ -9501,14 +8429,12 @@
         <v>65</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C156" s="1">
-        <f>[1]Sheet1!BO63</f>
         <v>1.5</v>
       </c>
       <c r="D156">
-        <f>C156*2</f>
         <v>3</v>
       </c>
       <c r="F156">
@@ -9553,14 +8479,12 @@
         <v>65</v>
       </c>
       <c r="B157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157" s="1">
-        <f>[1]Sheet1!BP63</f>
         <v>2.5</v>
       </c>
       <c r="D157">
-        <f>C157*2</f>
         <v>5</v>
       </c>
       <c r="F157">
@@ -9605,14 +8529,12 @@
         <v>65</v>
       </c>
       <c r="B158">
+        <v>6</v>
+      </c>
+      <c r="C158" s="1">
         <v>3</v>
       </c>
-      <c r="C158" s="1">
-        <f>[1]Sheet1!BQ63</f>
-        <v>3</v>
-      </c>
       <c r="D158">
-        <f>C158*2</f>
         <v>6</v>
       </c>
       <c r="F158">
@@ -9657,14 +8579,12 @@
         <v>66</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C159" s="1">
-        <f>[1]Sheet1!BO64</f>
         <v>2</v>
       </c>
       <c r="D159">
-        <f>C159*2</f>
         <v>4</v>
       </c>
       <c r="F159">
@@ -9709,14 +8629,12 @@
         <v>66</v>
       </c>
       <c r="B160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C160" s="1">
-        <f>[1]Sheet1!BP64</f>
         <v>3</v>
       </c>
       <c r="D160">
-        <f>C160*2</f>
         <v>6</v>
       </c>
       <c r="F160">
@@ -9761,14 +8679,12 @@
         <v>66</v>
       </c>
       <c r="B161">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C161" s="1">
-        <f>[1]Sheet1!BQ64</f>
         <v>3.5</v>
       </c>
       <c r="D161">
-        <f>C161*2</f>
         <v>7</v>
       </c>
       <c r="F161">
@@ -9813,14 +8729,12 @@
         <v>67</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C162" s="1">
-        <f>[1]Sheet1!BO65</f>
         <v>0.5</v>
       </c>
       <c r="D162">
-        <f>C162*2</f>
         <v>1</v>
       </c>
       <c r="F162">
@@ -9865,14 +8779,12 @@
         <v>67</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C163" s="1">
-        <f>[1]Sheet1!BP65</f>
         <v>0.8</v>
       </c>
       <c r="D163">
-        <f>C163*2</f>
         <v>1.6</v>
       </c>
       <c r="F163">
@@ -9917,14 +8829,12 @@
         <v>67</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C164" s="1">
-        <f>[1]Sheet1!BQ65</f>
         <v>1</v>
       </c>
       <c r="D164">
-        <f>C164*2</f>
         <v>2</v>
       </c>
       <c r="F164">
@@ -9969,14 +8879,12 @@
         <v>67</v>
       </c>
       <c r="B165">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C165" s="1">
-        <f>[1]Sheet1!BR65</f>
         <v>0.2</v>
       </c>
       <c r="D165">
-        <f>C165*2</f>
         <v>0.4</v>
       </c>
       <c r="F165">
@@ -10021,15 +8929,13 @@
         <v>68</v>
       </c>
       <c r="B166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C166" s="1">
-        <f>[1]Sheet1!BO66</f>
+        <v>0.9</v>
+      </c>
+      <c r="D166">
         <v>1.8</v>
-      </c>
-      <c r="D166">
-        <f>C166*2</f>
-        <v>3.6</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -10070,18 +8976,16 @@
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167" s="1">
-        <f>[1]Sheet1!BO68</f>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D167">
-        <f>C167*2</f>
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -10122,18 +9026,16 @@
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B168">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C168" s="1">
-        <f>[1]Sheet1!BP68</f>
-        <v>1.2</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D168">
-        <f>C168*2</f>
-        <v>2.4</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -10174,18 +9076,16 @@
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C169" s="1">
-        <f>[1]Sheet1!BQ68</f>
-        <v>1.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="D169">
-        <f>C169*2</f>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -10229,15 +9129,13 @@
         <v>69</v>
       </c>
       <c r="B170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C170" s="1">
-        <f>[1]Sheet1!BR68</f>
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="D170">
-        <f>C170*2</f>
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -10278,18 +9176,16 @@
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B171">
         <v>1</v>
       </c>
       <c r="C171" s="1">
-        <f>[1]Sheet1!BO69</f>
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="D171">
-        <f>C171*2</f>
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -10330,18 +9226,16 @@
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B172">
+        <v>6</v>
+      </c>
+      <c r="C172" s="1">
         <v>2</v>
       </c>
-      <c r="C172" s="1">
-        <f>[1]Sheet1!BP69</f>
-        <v>1.7</v>
-      </c>
       <c r="D172">
-        <f>C172*2</f>
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -10382,18 +9276,16 @@
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C173" s="1">
-        <f>[1]Sheet1!BQ69</f>
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="D173">
-        <f>C173*2</f>
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -10437,15 +9329,13 @@
         <v>70</v>
       </c>
       <c r="B174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C174" s="1">
-        <f>[1]Sheet1!BR69</f>
-        <v>0.7</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="D174">
-        <f>C174*2</f>
-        <v>1.4</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -10486,18 +9376,16 @@
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B175">
         <v>1</v>
       </c>
       <c r="C175" s="1">
-        <f>[1]Sheet1!BO70</f>
-        <v>1.7000000000000002</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D175">
-        <f>C175*2</f>
-        <v>3.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -10538,18 +9426,16 @@
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B176">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C176" s="1">
-        <f>[1]Sheet1!BP70</f>
-        <v>2.2999999999999998</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D176">
-        <f>C176*2</f>
-        <v>4.5999999999999996</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -10590,18 +9476,16 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B177">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C177" s="1">
-        <f>[1]Sheet1!BQ70</f>
-        <v>2.8000000000000003</v>
+        <v>0.9</v>
       </c>
       <c r="D177">
-        <f>C177*2</f>
-        <v>5.6000000000000005</v>
+        <v>1.8</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -10645,15 +9529,13 @@
         <v>71</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C178" s="1">
-        <f>[1]Sheet1!BR70</f>
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="D178">
-        <f>C178*2</f>
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -10694,18 +9576,16 @@
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179" s="1">
-        <f>[1]Sheet1!BO71</f>
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D179">
-        <f>C179*2</f>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -10746,18 +9626,16 @@
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B180">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C180" s="1">
-        <f>[1]Sheet1!BP71</f>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D180">
-        <f>C180*2</f>
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -10804,12 +9682,10 @@
         <v>3</v>
       </c>
       <c r="C181" s="1">
-        <f>[1]Sheet1!BQ71</f>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D181">
-        <f>C181*2</f>
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -10850,18 +9726,16 @@
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" s="1">
-        <f>[1]Sheet1!BO72</f>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D182">
-        <f>C182*2</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -10905,15 +9779,13 @@
         <v>73</v>
       </c>
       <c r="B183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C183" s="1">
-        <f>[1]Sheet1!BR72</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D183">
-        <f>C183*2</f>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -10954,18 +9826,16 @@
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184" s="1">
-        <f>[1]Sheet1!BO73</f>
+        <v>0.1</v>
+      </c>
+      <c r="D184">
         <v>0.2</v>
-      </c>
-      <c r="D184">
-        <f>C184*2</f>
-        <v>0.4</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -11009,15 +9879,13 @@
         <v>74</v>
       </c>
       <c r="B185">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C185" s="1">
-        <f>[1]Sheet1!BR73</f>
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="D185">
-        <f>C185*2</f>
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -11058,18 +9926,16 @@
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C186" s="1">
-        <f>[1]Sheet1!BO74</f>
+        <v>0.3</v>
+      </c>
+      <c r="D186">
         <v>0.6</v>
-      </c>
-      <c r="D186">
-        <f>C186*2</f>
-        <v>1.2</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -11113,14 +9979,12 @@
         <v>75</v>
       </c>
       <c r="B187">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C187" s="1">
-        <f>[1]Sheet1!BR74</f>
         <v>0.3</v>
       </c>
       <c r="D187">
-        <f>C187*2</f>
         <v>0.6</v>
       </c>
       <c r="F187">
@@ -11162,18 +10026,16 @@
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C188" s="1">
-        <f>[1]Sheet1!BO75</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D188">
-        <f>C188*2</f>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -11217,15 +10079,13 @@
         <v>76</v>
       </c>
       <c r="B189">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C189" s="1">
-        <f>[1]Sheet1!BR75</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D189">
-        <f>C189*2</f>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -11266,18 +10126,16 @@
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190" s="1">
-        <f>[1]Sheet1!BO76</f>
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D190">
-        <f>C190*2</f>
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -11318,18 +10176,16 @@
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B191">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C191" s="1">
-        <f>[1]Sheet1!BP76</f>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D191">
-        <f>C191*2</f>
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -11370,18 +10226,16 @@
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B192">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C192" s="1">
-        <f>[1]Sheet1!BQ76</f>
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="D192">
-        <f>C192*2</f>
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -11425,15 +10279,13 @@
         <v>77</v>
       </c>
       <c r="B193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C193" s="1">
-        <f>[1]Sheet1!BR76</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D193">
-        <f>C193*2</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -11474,18 +10326,16 @@
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B194">
         <v>1</v>
       </c>
       <c r="C194" s="1">
-        <f>[1]Sheet1!BO77</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D194">
-        <f>C194*2</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F194">
         <v>1</v>
@@ -11526,18 +10376,16 @@
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B195">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C195" s="1">
-        <f>[1]Sheet1!BP77</f>
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D195">
-        <f>C195*2</f>
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -11578,18 +10426,16 @@
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C196" s="1">
-        <f>[1]Sheet1!BQ77</f>
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="D196">
-        <f>C196*2</f>
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -11633,15 +10479,13 @@
         <v>78</v>
       </c>
       <c r="B197">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C197" s="1">
-        <f>[1]Sheet1!BR77</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D197">
-        <f>C197*2</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F197">
         <v>1</v>
@@ -11682,18 +10526,16 @@
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B198">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C198" s="1">
-        <f>[1]Sheet1!BO78</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D198">
-        <f>C198*2</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F198">
         <v>1</v>
@@ -11740,11 +10582,9 @@
         <v>3</v>
       </c>
       <c r="C199" s="1">
-        <f>[1]Sheet1!BQ78</f>
         <v>0.4</v>
       </c>
       <c r="D199">
-        <f>C199*2</f>
         <v>0.8</v>
       </c>
       <c r="F199">
@@ -11786,18 +10626,16 @@
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C200" s="1">
-        <f>[1]Sheet1!BO79</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D200">
-        <f>C200*2</f>
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F200">
         <v>1</v>
@@ -11844,12 +10682,10 @@
         <v>3</v>
       </c>
       <c r="C201" s="1">
-        <f>[1]Sheet1!BQ79</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D201">
-        <f>C201*2</f>
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -11890,18 +10726,16 @@
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C202" s="1">
-        <f>[1]Sheet1!BO80</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D202">
-        <f>C202*2</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -11948,12 +10782,10 @@
         <v>3</v>
       </c>
       <c r="C203" s="1">
-        <f>[1]Sheet1!BQ80</f>
+        <v>1</v>
+      </c>
+      <c r="D203">
         <v>2</v>
-      </c>
-      <c r="D203">
-        <f>C203*2</f>
-        <v>4</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -11994,18 +10826,16 @@
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C204" s="1">
-        <f>[1]Sheet1!BO81</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204">
-        <f>C204*2</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F204">
         <v>1</v>
@@ -12052,12 +10882,10 @@
         <v>3</v>
       </c>
       <c r="C205" s="1">
-        <f>[1]Sheet1!BQ81</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D205">
-        <f>C205*2</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -12098,18 +10926,16 @@
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C206" s="1">
-        <f>[1]Sheet1!BO82</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D206">
-        <f>C206*2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F206">
         <v>1</v>
@@ -12150,18 +10976,16 @@
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C207" s="1">
-        <f>[1]Sheet1!BQ82</f>
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="D207">
-        <f>C207*2</f>
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="F207">
         <v>1</v>
@@ -12205,15 +11029,13 @@
         <v>83</v>
       </c>
       <c r="B208">
+        <v>3</v>
+      </c>
+      <c r="C208" s="1">
+        <v>2</v>
+      </c>
+      <c r="D208">
         <v>4</v>
-      </c>
-      <c r="C208" s="1">
-        <f>[1]Sheet1!BR82</f>
-        <v>0.7</v>
-      </c>
-      <c r="D208">
-        <f>C208*2</f>
-        <v>1.4</v>
       </c>
       <c r="F208">
         <v>1</v>
@@ -12254,18 +11076,16 @@
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C209" s="1">
-        <f>[1]Sheet1!BO83</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D209">
-        <f>C209*2</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -12306,18 +11126,16 @@
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C210" s="1">
-        <f>[1]Sheet1!BQ83</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D210">
-        <f>C210*2</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F210">
         <v>1</v>
@@ -12361,15 +11179,13 @@
         <v>84</v>
       </c>
       <c r="B211">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C211" s="1">
-        <f>[1]Sheet1!BR83</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D211">
-        <f>C211*2</f>
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="F211">
         <v>1</v>
@@ -12410,18 +11226,16 @@
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C212" s="1">
-        <f>[1]Sheet1!BO84</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D212">
-        <f>C212*2</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -12462,18 +11276,16 @@
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B213">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C213" s="1">
-        <f>[1]Sheet1!BQ84</f>
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D213">
-        <f>C213*2</f>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -12514,18 +11326,17 @@
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B214">
-        <v>4</v>
-      </c>
-      <c r="C214" s="1">
-        <f>[1]Sheet1!BR84</f>
-        <v>0.1</v>
+        <v>3</v>
+      </c>
+      <c r="C214">
+        <v>3.3</v>
       </c>
       <c r="D214">
         <f>C214*2</f>
-        <v>0.2</v>
+        <v>6.6</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -12564,7 +11375,160 @@
         <v>0</v>
       </c>
     </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>87</v>
+      </c>
+      <c r="B215">
+        <v>3</v>
+      </c>
+      <c r="C215">
+        <v>5.5</v>
+      </c>
+      <c r="D215">
+        <f t="shared" ref="D215:D216" si="0">C215*2</f>
+        <v>11</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>0</v>
+      </c>
+      <c r="O215">
+        <v>0</v>
+      </c>
+      <c r="P215">
+        <v>0</v>
+      </c>
+      <c r="Q215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>88</v>
+      </c>
+      <c r="B216">
+        <v>3</v>
+      </c>
+      <c r="C216">
+        <v>6.5</v>
+      </c>
+      <c r="D216">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>0</v>
+      </c>
+      <c r="O216">
+        <v>0</v>
+      </c>
+      <c r="P216">
+        <v>0</v>
+      </c>
+      <c r="Q216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>85</v>
+      </c>
+      <c r="B217">
+        <v>3</v>
+      </c>
+      <c r="C217" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="D217">
+        <v>3.6</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>0</v>
+      </c>
+      <c r="O217">
+        <v>0</v>
+      </c>
+      <c r="P217">
+        <v>0</v>
+      </c>
+      <c r="Q217">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:R213" xr:uid="{66F9F789-5046-43B1-9C3D-7BC06BA3325B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>